--- a/Bases_de_Dados/FootyStats/Scotland Premiership_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Scotland Premiership_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP171"/>
+  <dimension ref="A1:BP172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AQ10" t="n">
         <v>0.67</v>
@@ -2876,7 +2876,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -4835,10 +4835,10 @@
         <v>3</v>
       </c>
       <c r="AP20" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AR20" t="n">
         <v>2.24</v>
@@ -5925,7 +5925,7 @@
         <v>3</v>
       </c>
       <c r="AP25" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AQ25" t="n">
         <v>1.86</v>
@@ -6800,7 +6800,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AR29" t="n">
         <v>1.22</v>
@@ -10285,7 +10285,7 @@
         <v>1.67</v>
       </c>
       <c r="AP45" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AQ45" t="n">
         <v>1.07</v>
@@ -11378,7 +11378,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AR50" t="n">
         <v>0.86</v>
@@ -12250,7 +12250,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AR54" t="n">
         <v>1.79</v>
@@ -12683,7 +12683,7 @@
         <v>1.67</v>
       </c>
       <c r="AP56" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AQ56" t="n">
         <v>0.6</v>
@@ -16607,7 +16607,7 @@
         <v>0.57</v>
       </c>
       <c r="AP74" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AQ74" t="n">
         <v>0.36</v>
@@ -16828,7 +16828,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ75" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AR75" t="n">
         <v>1.27</v>
@@ -18136,7 +18136,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AR81" t="n">
         <v>1.94</v>
@@ -18351,7 +18351,7 @@
         <v>1.5</v>
       </c>
       <c r="AP82" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AQ82" t="n">
         <v>1.36</v>
@@ -22057,7 +22057,7 @@
         <v>1.5</v>
       </c>
       <c r="AP99" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AQ99" t="n">
         <v>1.33</v>
@@ -22278,7 +22278,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AR100" t="n">
         <v>1.55</v>
@@ -24022,7 +24022,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AR108" t="n">
         <v>1.27</v>
@@ -24237,7 +24237,7 @@
         <v>1.33</v>
       </c>
       <c r="AP109" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AQ109" t="n">
         <v>1.46</v>
@@ -25327,7 +25327,7 @@
         <v>0.71</v>
       </c>
       <c r="AP114" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AQ114" t="n">
         <v>0.5</v>
@@ -25984,7 +25984,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ117" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AR117" t="n">
         <v>1.61</v>
@@ -27507,7 +27507,7 @@
         <v>1.2</v>
       </c>
       <c r="AP124" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AQ124" t="n">
         <v>0.87</v>
@@ -29036,7 +29036,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ131" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AR131" t="n">
         <v>1.42</v>
@@ -30344,7 +30344,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ137" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AR137" t="n">
         <v>1.74</v>
@@ -30559,7 +30559,7 @@
         <v>0.55</v>
       </c>
       <c r="AP138" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AQ138" t="n">
         <v>0.67</v>
@@ -32739,7 +32739,7 @@
         <v>0.67</v>
       </c>
       <c r="AP148" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AQ148" t="n">
         <v>0.6</v>
@@ -34704,7 +34704,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ157" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AR157" t="n">
         <v>1.44</v>
@@ -35137,7 +35137,7 @@
         <v>2</v>
       </c>
       <c r="AP159" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AQ159" t="n">
         <v>1.86</v>
@@ -37556,13 +37556,13 @@
         <v>0</v>
       </c>
       <c r="AW170" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX170" t="n">
         <v>5</v>
       </c>
       <c r="AY170" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ170" t="n">
         <v>5</v>
@@ -37832,6 +37832,224 @@
       </c>
       <c r="BP171" t="n">
         <v>1.52</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" t="n">
+        <v>8206310</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Scotland Premiership</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="n">
+        <v>46082.375</v>
+      </c>
+      <c r="F172" t="n">
+        <v>29</v>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Rangers</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Celtic</t>
+        </is>
+      </c>
+      <c r="I172" t="n">
+        <v>2</v>
+      </c>
+      <c r="J172" t="n">
+        <v>0</v>
+      </c>
+      <c r="K172" t="n">
+        <v>2</v>
+      </c>
+      <c r="L172" t="n">
+        <v>2</v>
+      </c>
+      <c r="M172" t="n">
+        <v>2</v>
+      </c>
+      <c r="N172" t="n">
+        <v>4</v>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>['8', '26']</t>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>['56', '90+1']</t>
+        </is>
+      </c>
+      <c r="Q172" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R172" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="S172" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T172" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U172" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="V172" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="W172" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X172" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="Y172" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z172" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AA172" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AB172" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AC172" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD172" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE172" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF172" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG172" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH172" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI172" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AJ172" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AK172" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL172" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM172" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN172" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AO172" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AP172" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AQ172" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AR172" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS172" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AT172" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="AU172" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV172" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW172" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX172" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY172" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ172" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA172" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB172" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC172" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD172" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BE172" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF172" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BG172" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH172" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI172" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BJ172" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BK172" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BL172" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BM172" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BN172" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BO172" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BP172" t="n">
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Scotland Premiership_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Scotland Premiership_20252026.xlsx
@@ -36902,13 +36902,13 @@
         <v>3</v>
       </c>
       <c r="AW167" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX167" t="n">
         <v>4</v>
       </c>
       <c r="AY167" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ167" t="n">
         <v>7</v>
@@ -37338,13 +37338,13 @@
         <v>3</v>
       </c>
       <c r="AW169" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX169" t="n">
         <v>3</v>
       </c>
       <c r="AY169" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ169" t="n">
         <v>6</v>
@@ -37777,13 +37777,13 @@
         <v>7</v>
       </c>
       <c r="AX171" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY171" t="n">
         <v>10</v>
       </c>
       <c r="AZ171" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA171" t="n">
         <v>7</v>

--- a/Bases_de_Dados/FootyStats/Scotland Premiership_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Scotland Premiership_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP172"/>
+  <dimension ref="A1:BP174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1786,7 +1786,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AQ12" t="n">
         <v>1.86</v>
@@ -4838,7 +4838,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR20" t="n">
         <v>2.24</v>
@@ -5274,7 +5274,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR22" t="n">
         <v>1.61</v>
@@ -5489,7 +5489,7 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ23" t="n">
         <v>1.36</v>
@@ -5707,7 +5707,7 @@
         <v>0.5</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ24" t="n">
         <v>0.36</v>
@@ -6364,7 +6364,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR27" t="n">
         <v>1.58</v>
@@ -6800,7 +6800,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR29" t="n">
         <v>1.22</v>
@@ -7233,7 +7233,7 @@
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AQ31" t="n">
         <v>0.87</v>
@@ -7887,7 +7887,7 @@
         <v>1</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AQ34" t="n">
         <v>0.6</v>
@@ -8977,7 +8977,7 @@
         <v>0.5</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AQ39" t="n">
         <v>0.36</v>
@@ -9198,7 +9198,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR40" t="n">
         <v>1.22</v>
@@ -9849,7 +9849,7 @@
         <v>0.67</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ43" t="n">
         <v>0.67</v>
@@ -11378,7 +11378,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR50" t="n">
         <v>0.86</v>
@@ -11811,10 +11811,10 @@
         <v>1</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR52" t="n">
         <v>1.77</v>
@@ -12250,7 +12250,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR54" t="n">
         <v>1.79</v>
@@ -12465,7 +12465,7 @@
         <v>1.25</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ55" t="n">
         <v>1.33</v>
@@ -15517,7 +15517,7 @@
         <v>1.2</v>
       </c>
       <c r="AP69" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ69" t="n">
         <v>1.46</v>
@@ -16171,7 +16171,7 @@
         <v>1.2</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AQ72" t="n">
         <v>1.36</v>
@@ -16828,7 +16828,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ75" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR75" t="n">
         <v>1.27</v>
@@ -17043,7 +17043,7 @@
         <v>2.6</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ76" t="n">
         <v>1.86</v>
@@ -17700,7 +17700,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ79" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR79" t="n">
         <v>0.9399999999999999</v>
@@ -18136,7 +18136,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR81" t="n">
         <v>1.94</v>
@@ -19005,7 +19005,7 @@
         <v>2</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AQ85" t="n">
         <v>1.79</v>
@@ -19659,10 +19659,10 @@
         <v>0.67</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ88" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR88" t="n">
         <v>1.28</v>
@@ -21185,7 +21185,7 @@
         <v>1.38</v>
       </c>
       <c r="AP95" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AQ95" t="n">
         <v>1.46</v>
@@ -21839,7 +21839,7 @@
         <v>0.86</v>
       </c>
       <c r="AP98" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ98" t="n">
         <v>0.6</v>
@@ -22275,10 +22275,10 @@
         <v>1.86</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR100" t="n">
         <v>1.55</v>
@@ -22711,7 +22711,7 @@
         <v>1.33</v>
       </c>
       <c r="AP102" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AQ102" t="n">
         <v>1.33</v>
@@ -24022,7 +24022,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR108" t="n">
         <v>1.27</v>
@@ -24891,7 +24891,7 @@
         <v>1</v>
       </c>
       <c r="AP112" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ112" t="n">
         <v>1.07</v>
@@ -25330,7 +25330,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ114" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR114" t="n">
         <v>1.91</v>
@@ -25984,7 +25984,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ117" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR117" t="n">
         <v>1.61</v>
@@ -26417,7 +26417,7 @@
         <v>0.3</v>
       </c>
       <c r="AP119" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AQ119" t="n">
         <v>0.67</v>
@@ -26856,7 +26856,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ121" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR121" t="n">
         <v>1.59</v>
@@ -28815,7 +28815,7 @@
         <v>1.9</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ130" t="n">
         <v>1.79</v>
@@ -29036,7 +29036,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ131" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR131" t="n">
         <v>1.42</v>
@@ -29254,7 +29254,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ132" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR132" t="n">
         <v>1.73</v>
@@ -29472,7 +29472,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ133" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR133" t="n">
         <v>1.33</v>
@@ -29687,7 +29687,7 @@
         <v>0.36</v>
       </c>
       <c r="AP134" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ134" t="n">
         <v>0.36</v>
@@ -30344,7 +30344,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ137" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR137" t="n">
         <v>1.74</v>
@@ -31431,7 +31431,7 @@
         <v>2.09</v>
       </c>
       <c r="AP142" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AQ142" t="n">
         <v>1.86</v>
@@ -33614,7 +33614,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ152" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR152" t="n">
         <v>1.39</v>
@@ -34486,7 +34486,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ156" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR156" t="n">
         <v>1.76</v>
@@ -34704,7 +34704,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ157" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR157" t="n">
         <v>1.44</v>
@@ -35355,7 +35355,7 @@
         <v>0.5</v>
       </c>
       <c r="AP160" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ160" t="n">
         <v>0.67</v>
@@ -35791,7 +35791,7 @@
         <v>0.62</v>
       </c>
       <c r="AP162" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AQ162" t="n">
         <v>0.6</v>
@@ -36663,7 +36663,7 @@
         <v>0.92</v>
       </c>
       <c r="AP166" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AQ166" t="n">
         <v>0.87</v>
@@ -37756,7 +37756,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ171" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR171" t="n">
         <v>1.23</v>
@@ -37974,7 +37974,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ172" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR172" t="n">
         <v>2.02</v>
@@ -38050,6 +38050,442 @@
       </c>
       <c r="BP172" t="n">
         <v>1.42</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" t="n">
+        <v>8206160</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Scotland Premiership</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="n">
+        <v>46084.69791666666</v>
+      </c>
+      <c r="F173" t="n">
+        <v>23</v>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>St. Mirren</t>
+        </is>
+      </c>
+      <c r="I173" t="n">
+        <v>1</v>
+      </c>
+      <c r="J173" t="n">
+        <v>0</v>
+      </c>
+      <c r="K173" t="n">
+        <v>1</v>
+      </c>
+      <c r="L173" t="n">
+        <v>2</v>
+      </c>
+      <c r="M173" t="n">
+        <v>1</v>
+      </c>
+      <c r="N173" t="n">
+        <v>3</v>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>['8', '83']</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>['47']</t>
+        </is>
+      </c>
+      <c r="Q173" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R173" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="S173" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T173" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U173" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V173" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="W173" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X173" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y173" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z173" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA173" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB173" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC173" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD173" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AE173" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF173" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AG173" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH173" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AI173" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ173" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AK173" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL173" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM173" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AN173" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AO173" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP173" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ173" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="AR173" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS173" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AT173" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AU173" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV173" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW173" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX173" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY173" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ173" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA173" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB173" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC173" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD173" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BE173" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF173" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG173" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH173" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI173" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BJ173" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BK173" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BL173" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BM173" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BN173" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BO173" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BP173" t="n">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" t="n">
+        <v>8206199</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Scotland Premiership</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="n">
+        <v>46085.70833333334</v>
+      </c>
+      <c r="F174" t="n">
+        <v>25</v>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Celtic</t>
+        </is>
+      </c>
+      <c r="I174" t="n">
+        <v>1</v>
+      </c>
+      <c r="J174" t="n">
+        <v>1</v>
+      </c>
+      <c r="K174" t="n">
+        <v>2</v>
+      </c>
+      <c r="L174" t="n">
+        <v>1</v>
+      </c>
+      <c r="M174" t="n">
+        <v>2</v>
+      </c>
+      <c r="N174" t="n">
+        <v>3</v>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>['19']</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>['5', '67']</t>
+        </is>
+      </c>
+      <c r="Q174" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="R174" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S174" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="T174" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U174" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="V174" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="W174" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X174" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="Y174" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z174" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA174" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AB174" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC174" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD174" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE174" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF174" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AG174" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH174" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AI174" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ174" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK174" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM174" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AN174" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AO174" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AP174" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ174" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR174" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AS174" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AT174" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AU174" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV174" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW174" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX174" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY174" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ174" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA174" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB174" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC174" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD174" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BE174" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF174" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BG174" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BH174" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BI174" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BJ174" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="BK174" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BL174" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BM174" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BN174" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BO174" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BP174" t="n">
+        <v>1.61</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Scotland Premiership_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Scotland Premiership_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP174"/>
+  <dimension ref="A1:BP175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ5" t="n">
         <v>1.33</v>
@@ -2440,7 +2440,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -3748,7 +3748,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR15" t="n">
         <v>1.39</v>
@@ -5053,7 +5053,7 @@
         <v>1</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ21" t="n">
         <v>1.07</v>
@@ -6143,10 +6143,10 @@
         <v>1</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR26" t="n">
         <v>0.53</v>
@@ -7015,7 +7015,7 @@
         <v>0.67</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ30" t="n">
         <v>0.36</v>
@@ -9634,7 +9634,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR42" t="n">
         <v>2.37</v>
@@ -11375,7 +11375,7 @@
         <v>2.33</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ50" t="n">
         <v>1.8</v>
@@ -12032,7 +12032,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR53" t="n">
         <v>0.95</v>
@@ -15299,7 +15299,7 @@
         <v>1.8</v>
       </c>
       <c r="AP68" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ68" t="n">
         <v>1.79</v>
@@ -15520,7 +15520,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR69" t="n">
         <v>1.48</v>
@@ -16392,7 +16392,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR73" t="n">
         <v>1.2</v>
@@ -17697,7 +17697,7 @@
         <v>0.8</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ79" t="n">
         <v>0.47</v>
@@ -19226,7 +19226,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR86" t="n">
         <v>1.42</v>
@@ -20095,7 +20095,7 @@
         <v>1.5</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ90" t="n">
         <v>0.87</v>
@@ -21188,7 +21188,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ95" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR95" t="n">
         <v>1.65</v>
@@ -24240,7 +24240,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ109" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR109" t="n">
         <v>1.76</v>
@@ -24455,7 +24455,7 @@
         <v>1.44</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ110" t="n">
         <v>1.36</v>
@@ -25109,7 +25109,7 @@
         <v>0.78</v>
       </c>
       <c r="AP113" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ113" t="n">
         <v>0.6</v>
@@ -28164,7 +28164,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ127" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR127" t="n">
         <v>1.76</v>
@@ -28597,7 +28597,7 @@
         <v>2</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ129" t="n">
         <v>1.86</v>
@@ -30780,7 +30780,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ139" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR139" t="n">
         <v>1.33</v>
@@ -34047,7 +34047,7 @@
         <v>0.31</v>
       </c>
       <c r="AP154" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ154" t="n">
         <v>0.36</v>
@@ -36012,7 +36012,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ163" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR163" t="n">
         <v>1.44</v>
@@ -37099,7 +37099,7 @@
         <v>1.36</v>
       </c>
       <c r="AP168" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ168" t="n">
         <v>1.33</v>
@@ -38486,6 +38486,224 @@
       </c>
       <c r="BP174" t="n">
         <v>1.61</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" t="n">
+        <v>8206273</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Scotland Premiership</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="n">
+        <v>46088.5</v>
+      </c>
+      <c r="F175" t="n">
+        <v>25</v>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Dundee</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Motherwell</t>
+        </is>
+      </c>
+      <c r="I175" t="n">
+        <v>1</v>
+      </c>
+      <c r="J175" t="n">
+        <v>0</v>
+      </c>
+      <c r="K175" t="n">
+        <v>1</v>
+      </c>
+      <c r="L175" t="n">
+        <v>2</v>
+      </c>
+      <c r="M175" t="n">
+        <v>1</v>
+      </c>
+      <c r="N175" t="n">
+        <v>3</v>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>['32', '84']</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>['78']</t>
+        </is>
+      </c>
+      <c r="Q175" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R175" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="S175" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T175" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U175" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="V175" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="W175" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X175" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y175" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z175" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="AA175" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB175" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AC175" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD175" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AE175" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF175" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AG175" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AH175" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AI175" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AJ175" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AK175" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM175" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN175" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AO175" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AP175" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ175" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR175" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AS175" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AT175" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AU175" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV175" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW175" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX175" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY175" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ175" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA175" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB175" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC175" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD175" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BE175" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF175" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BG175" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BH175" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI175" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BJ175" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BK175" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BL175" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BM175" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BN175" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BO175" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP175" t="n">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Scotland Premiership_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Scotland Premiership_20252026.xlsx
@@ -38646,25 +38646,25 @@
         <v>9</v>
       </c>
       <c r="AW175" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX175" t="n">
         <v>12</v>
       </c>
       <c r="AY175" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ175" t="n">
         <v>21</v>
       </c>
       <c r="BA175" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB175" t="n">
         <v>1</v>
       </c>
       <c r="BC175" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BD175" t="n">
         <v>2.55</v>
